--- a/data/trans_camb/MCS12_SP_R3-Edad-trans_camb.xlsx
+++ b/data/trans_camb/MCS12_SP_R3-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población en el primer cuartil (48.388) de la puntuación del componente de salud mental (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 8,56</t>
+          <t>-0,5; 8,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 3,68</t>
+          <t>-5,1; 3,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 2,01</t>
+          <t>-8,83; 1,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 5,04</t>
+          <t>-5,52; 5,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,98; -1,28</t>
+          <t>-10,68; -0,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 10,26</t>
+          <t>-4,57; 10,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 5,35</t>
+          <t>-1,73; 5,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 0,28</t>
+          <t>-6,34; 0,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 2,93</t>
+          <t>-5,7; 3,27</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 86,07</t>
+          <t>-3,91; 86,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,37; 36,62</t>
+          <t>-36,19; 35,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,28; 21,11</t>
+          <t>-66,67; 20,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,26; 32,12</t>
+          <t>-27,18; 32,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,34; -7,22</t>
+          <t>-51,02; -5,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,32; 65,7</t>
+          <t>-23,24; 61,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 39,03</t>
+          <t>-10,37; 38,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,2; 1,79</t>
+          <t>-38,72; 1,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 21,03</t>
+          <t>-35,48; 24,38</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 9,01</t>
+          <t>0,73; 9,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 6,15</t>
+          <t>-1,47; 6,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 3,87</t>
+          <t>-6,01; 3,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 6,4</t>
+          <t>-3,3; 6,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 0,43</t>
+          <t>-8,68; -0,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 1,58</t>
+          <t>-11,89; 1,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 6,57</t>
+          <t>0,05; 6,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 2,56</t>
+          <t>-3,7; 2,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 1,33</t>
+          <t>-6,37; 1,68</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,74; 79,58</t>
+          <t>4,84; 77,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 52,91</t>
+          <t>-9,79; 52,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,11; 32,48</t>
+          <t>-41,09; 31,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 32,27</t>
+          <t>-13,55; 32,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,81; 2,57</t>
+          <t>-36,24; 0,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,84; 8,27</t>
+          <t>-52,62; 7,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 41,36</t>
+          <t>0,34; 39,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 16,53</t>
+          <t>-20,01; 14,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-37,86; 8,21</t>
+          <t>-35,18; 10,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 6,42</t>
+          <t>-3,37; 6,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 0,46</t>
+          <t>-7,87; 0,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 1,67</t>
+          <t>-8,13; 1,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,55; 13,04</t>
+          <t>2,76; 13,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 2,26</t>
+          <t>-7,02; 2,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,37; -0,68</t>
+          <t>-9,17; -0,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 8,46</t>
+          <t>1,54; 8,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 0,1</t>
+          <t>-6,4; 0,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,35; -0,94</t>
+          <t>-7,42; -0,64</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 34,52</t>
+          <t>-14,01; 32,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,13; 2,47</t>
+          <t>-34,34; 4,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-33,92; 8,78</t>
+          <t>-34,56; 5,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,02; 57,72</t>
+          <t>9,95; 58,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,91; 10,41</t>
+          <t>-25,85; 8,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,67; -2,13</t>
+          <t>-33,86; -4,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,02; 39,2</t>
+          <t>5,88; 38,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-25,5; 0,48</t>
+          <t>-25,77; 1,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-29,44; -4,22</t>
+          <t>-29,95; -4,04</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 10,4</t>
+          <t>0,15; 10,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 11,06</t>
+          <t>0,72; 10,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 7,44</t>
+          <t>-11,49; 7,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 10,74</t>
+          <t>-1,22; 10,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 5,01</t>
+          <t>-6,0; 4,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,11; -0,27</t>
+          <t>-10,8; -0,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 8,65</t>
+          <t>1,34; 9,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 6,25</t>
+          <t>-0,7; 6,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 1,14</t>
+          <t>-12,05; 1,52</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,49; 74,64</t>
+          <t>0,75; 70,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,42; 77,48</t>
+          <t>3,17; 71,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,89; 46,37</t>
+          <t>-62,67; 47,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 38,95</t>
+          <t>-3,5; 38,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 17,24</t>
+          <t>-17,4; 18,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,59; -0,98</t>
+          <t>-32,74; -0,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,71; 40,17</t>
+          <t>5,14; 40,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 28,6</t>
+          <t>-2,54; 31,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,47; 4,82</t>
+          <t>-50,15; 6,46</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 7,63</t>
+          <t>-4,77; 8,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 2,26</t>
+          <t>-9,23; 2,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 4,35</t>
+          <t>-6,46; 4,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 13,77</t>
+          <t>0,53; 13,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 7,16</t>
+          <t>-5,52; 7,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 3,67</t>
+          <t>-7,29; 3,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 8,64</t>
+          <t>-0,03; 8,9</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 3,2</t>
+          <t>-5,5; 2,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 2,27</t>
+          <t>-5,24; 2,22</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,97; 34,64</t>
+          <t>-16,8; 37,5</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-32,78; 10,34</t>
+          <t>-33,29; 11,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,99; 19,97</t>
+          <t>-22,41; 21,82</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,27; 45,95</t>
+          <t>1,35; 47,04</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 24,1</t>
+          <t>-15,28; 26,04</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-19,85; 12,87</t>
+          <t>-19,58; 12,94</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 31,87</t>
+          <t>-0,07; 33,33</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 11,71</t>
+          <t>-17,69; 9,89</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 8,54</t>
+          <t>-16,61; 8,79</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 5,97</t>
+          <t>-8,95; 5,64</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-15,03; -2,04</t>
+          <t>-15,86; -1,92</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 3,58</t>
+          <t>-8,6; 4,19</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 12,64</t>
+          <t>-1,15; 12,67</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 11,29</t>
+          <t>-2,58; 11,19</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 49,83</t>
+          <t>-1,24; 54,43</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 7,51</t>
+          <t>-2,42; 7,56</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 3,27</t>
+          <t>-6,6; 2,77</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 39,48</t>
+          <t>-2,18; 40,93</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-29,62; 25,5</t>
+          <t>-29,29; 24,19</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-49,98; -8,49</t>
+          <t>-51,51; -8,2</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-28,04; 15,91</t>
+          <t>-27,74; 18,97</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 45,84</t>
+          <t>-3,14; 46,4</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 40,9</t>
+          <t>-7,42; 40,82</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 194,86</t>
+          <t>-4,09; 228,44</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 28,53</t>
+          <t>-8,01; 27,99</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-22,26; 12,66</t>
+          <t>-21,55; 9,91</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 148,75</t>
+          <t>-7,26; 150,08</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 14,35</t>
+          <t>-3,86; 13,59</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 8,9</t>
+          <t>-5,96; 9,96</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 11,55</t>
+          <t>-2,81; 11,65</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6,73; 21,99</t>
+          <t>6,81; 21,85</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,1; 15,39</t>
+          <t>-0,94; 15,05</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,94; 17,92</t>
+          <t>4,83; 18,19</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,32; 16,61</t>
+          <t>5,41; 16,41</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 10,28</t>
+          <t>-1,14; 10,23</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4,08; 13,76</t>
+          <t>3,71; 13,51</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 64,73</t>
+          <t>-11,99; 58,77</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 38,33</t>
+          <t>-18,34; 46,48</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 50,95</t>
+          <t>-9,06; 51,34</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18,97; 80,13</t>
+          <t>18,44; 79,82</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,4; 56,18</t>
+          <t>-2,31; 54,65</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,85; 66,28</t>
+          <t>13,4; 68,56</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,12; 62,67</t>
+          <t>16,52; 61,81</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 38,3</t>
+          <t>-3,57; 37,56</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>12,11; 52,33</t>
+          <t>10,54; 49,34</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,63</t>
+          <t>1,68; 5,75</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 2,2</t>
+          <t>-1,66; 2,25</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 2,07</t>
+          <t>-5,14; 2,21</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,51</t>
+          <t>3,86; 8,42</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,46</t>
+          <t>-1,8; 2,43</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 17,54</t>
+          <t>-0,4; 18,28</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,43</t>
+          <t>3,38; 6,37</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,66</t>
+          <t>-1,27; 1,61</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 9,47</t>
+          <t>-1,02; 10,09</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>7,09; 31,83</t>
+          <t>8,72; 32,61</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 12,62</t>
+          <t>-8,52; 12,76</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 11,61</t>
+          <t>-26,14; 12,46</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13,78; 33,52</t>
+          <t>13,92; 32,96</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 9,84</t>
+          <t>-6,51; 9,52</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 71,67</t>
+          <t>-1,51; 72,14</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,31; 29,76</t>
+          <t>14,34; 29,08</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 7,66</t>
+          <t>-5,38; 7,45</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 42,23</t>
+          <t>-4,51; 45,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/MCS12_SP_R3-Edad-trans_camb.xlsx
+++ b/data/trans_camb/MCS12_SP_R3-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-4,24</t>
+          <t>-2,95</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,49</t>
+          <t>1,99</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,61</t>
+          <t>-0,74</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 8,44</t>
+          <t>-0,24; 8,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 3,57</t>
+          <t>-5,42; 3,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 1,9</t>
+          <t>-8,36; 2,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 5,19</t>
+          <t>-5,25; 4,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,68; -0,82</t>
+          <t>-10,76; -0,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 10,16</t>
+          <t>-4,83; 9,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 5,16</t>
+          <t>-1,17; 5,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 0,16</t>
+          <t>-6,8; -0,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 3,27</t>
+          <t>-5,07; 3,5</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-35,87%</t>
+          <t>-24,94%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-10,71%</t>
+          <t>-4,89%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 86,9</t>
+          <t>-4,02; 86,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 35,59</t>
+          <t>-39,95; 33,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-66,67; 20,76</t>
+          <t>-61,91; 27,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 32,43</t>
+          <t>-25,64; 31,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,02; -5,46</t>
+          <t>-50,12; -5,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 61,68</t>
+          <t>-24,74; 56,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 38,56</t>
+          <t>-7,15; 40,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 1,89</t>
+          <t>-39,96; -2,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,48; 24,38</t>
+          <t>-30,92; 25,19</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,5</t>
+          <t>-0,4</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,01</t>
+          <t>-1,42</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,13</t>
+          <t>-0,48</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 9,01</t>
+          <t>0,71; 8,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 6,26</t>
+          <t>-1,55; 6,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 3,54</t>
+          <t>-5,03; 4,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 6,47</t>
+          <t>-3,24; 6,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,68; -0,04</t>
+          <t>-8,36; 1,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 1,4</t>
+          <t>-5,94; 4,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 6,21</t>
+          <t>0,34; 6,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 2,23</t>
+          <t>-3,76; 2,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 1,68</t>
+          <t>-3,72; 3,2</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-11,33%</t>
+          <t>-3,01%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-18,49%</t>
+          <t>-6,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-12,47%</t>
+          <t>-2,8%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 77,86</t>
+          <t>4,43; 75,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 52,4</t>
+          <t>-10,65; 56,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,09; 31,95</t>
+          <t>-34,01; 35,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 32,85</t>
+          <t>-13,47; 33,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 0,28</t>
+          <t>-34,66; 5,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,62; 7,31</t>
+          <t>-25,65; 21,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 39,08</t>
+          <t>1,13; 40,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 14,66</t>
+          <t>-20,22; 15,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,18; 10,11</t>
+          <t>-20,24; 19,84</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,21</t>
+          <t>-3,93</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,86</t>
+          <t>-3,82</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-4,1</t>
+          <t>-3,94</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 6,02</t>
+          <t>-3,05; 6,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 0,84</t>
+          <t>-8,52; 0,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 1,05</t>
+          <t>-8,89; 0,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 13,11</t>
+          <t>3,44; 12,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 2,0</t>
+          <t>-7,04; 1,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,17; -0,97</t>
+          <t>-8,07; 0,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 8,33</t>
+          <t>1,79; 8,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 0,18</t>
+          <t>-6,33; 0,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,42; -0,64</t>
+          <t>-7,31; -1,0</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-15,16%</t>
+          <t>-18,57%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-19,51%</t>
+          <t>-15,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-17,75%</t>
+          <t>-17,06%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 32,08</t>
+          <t>-12,91; 32,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,34; 4,7</t>
+          <t>-35,71; 4,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,56; 5,92</t>
+          <t>-37,24; 2,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,95; 58,16</t>
+          <t>12,65; 57,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,85; 8,77</t>
+          <t>-25,93; 9,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,86; -4,41</t>
+          <t>-29,22; 0,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,88; 38,16</t>
+          <t>7,38; 40,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 1,13</t>
+          <t>-25,42; 0,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-29,95; -4,04</t>
+          <t>-29,04; -4,57</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,68</t>
+          <t>4,09</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-5,37</t>
+          <t>-4,39</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,51</t>
+          <t>-0,06</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 10,49</t>
+          <t>1,24; 10,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 10,6</t>
+          <t>1,17; 11,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 7,58</t>
+          <t>-0,6; 8,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 10,51</t>
+          <t>-1,05; 10,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 4,99</t>
+          <t>-6,34; 4,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,8; -0,2</t>
+          <t>-9,28; 0,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 9,06</t>
+          <t>0,86; 8,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 6,54</t>
+          <t>-1,26; 6,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 1,52</t>
+          <t>-3,16; 3,64</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-3,99%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-17,42%</t>
+          <t>-14,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-14,71%</t>
+          <t>-0,25%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,75; 70,18</t>
+          <t>4,73; 77,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,17; 71,7</t>
+          <t>5,5; 80,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-62,67; 47,89</t>
+          <t>-3,21; 63,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 38,81</t>
+          <t>-2,64; 37,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,4; 18,6</t>
+          <t>-18,29; 18,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,74; -0,95</t>
+          <t>-27,1; 0,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,14; 40,64</t>
+          <t>3,72; 40,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 31,19</t>
+          <t>-4,6; 29,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-50,15; 6,46</t>
+          <t>-11,88; 17,16</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,98</t>
+          <t>-1,23</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,64</t>
+          <t>-1,06</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,43</t>
+          <t>-1,22</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 8,33</t>
+          <t>-4,22; 7,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 2,56</t>
+          <t>-9,31; 2,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 4,64</t>
+          <t>-6,87; 4,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,53; 13,62</t>
+          <t>0,6; 14,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 7,55</t>
+          <t>-5,37; 7,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 3,69</t>
+          <t>-6,34; 4,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 8,9</t>
+          <t>-0,55; 8,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 2,7</t>
+          <t>-5,84; 3,04</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 2,22</t>
+          <t>-5,34; 2,33</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-3,93%</t>
+          <t>-4,91%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-5,0%</t>
+          <t>-3,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-4,92%</t>
+          <t>-4,2%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 37,5</t>
+          <t>-15,3; 33,77</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-33,29; 11,84</t>
+          <t>-33,36; 10,24</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 21,82</t>
+          <t>-23,34; 18,87</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,35; 47,04</t>
+          <t>1,44; 48,61</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 26,04</t>
+          <t>-14,95; 24,83</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-19,58; 12,94</t>
+          <t>-17,26; 16,21</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 33,33</t>
+          <t>-1,76; 32,38</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 9,89</t>
+          <t>-18,9; 10,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 8,79</t>
+          <t>-17,21; 8,79</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-2,19</t>
+          <t>-2,42</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,68</t>
+          <t>1,42</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14,3</t>
+          <t>-0,49</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 5,64</t>
+          <t>-8,57; 5,55</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-15,86; -1,92</t>
+          <t>-15,41; -2,16</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 4,19</t>
+          <t>-8,58; 3,36</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 12,67</t>
+          <t>-0,54; 13,27</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 11,19</t>
+          <t>-3,07; 10,96</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 54,43</t>
+          <t>-4,0; 7,43</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 7,56</t>
+          <t>-2,64; 7,13</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 2,77</t>
+          <t>-7,07; 2,66</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 40,93</t>
+          <t>-4,88; 4,11</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-8,1%</t>
+          <t>-8,97%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>-1,69%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 24,19</t>
+          <t>-29,26; 23,81</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-51,51; -8,2</t>
+          <t>-49,13; -8,58</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-27,74; 18,97</t>
+          <t>-27,68; 15,12</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 46,4</t>
+          <t>-1,63; 48,72</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 40,82</t>
+          <t>-8,73; 39,4</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 228,44</t>
+          <t>-11,57; 28,04</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 27,99</t>
+          <t>-8,62; 26,53</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-21,55; 9,91</t>
+          <t>-22,1; 9,38</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 150,08</t>
+          <t>-15,79; 15,68</t>
         </is>
       </c>
     </row>
@@ -1930,37 +1930,37 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>5,03</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>14,45</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>6,97</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>11,67</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>10,83</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>4,78</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>14,45</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>6,97</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>11,53</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>10,83</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>4,78</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8,74</t>
+          <t>8,91</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 13,59</t>
+          <t>-2,66; 14,4</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 9,96</t>
+          <t>-7,29; 8,64</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 11,65</t>
+          <t>-2,41; 12,19</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6,81; 21,85</t>
+          <t>6,95; 21,74</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 15,05</t>
+          <t>-1,23; 13,92</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,83; 18,19</t>
+          <t>4,68; 18,08</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,41; 16,41</t>
+          <t>5,31; 16,41</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 10,23</t>
+          <t>-0,62; 10,63</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,71; 13,51</t>
+          <t>3,49; 13,75</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,14 +2051,14 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t>36,63%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
           <t>36,18%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>36,18%</t>
-        </is>
-      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
           <t>15,96%</t>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 58,77</t>
+          <t>-8,52; 64,17</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 46,48</t>
+          <t>-22,6; 37,95</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 51,34</t>
+          <t>-7,53; 55,88</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18,44; 79,82</t>
+          <t>18,89; 80,01</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 54,65</t>
+          <t>-4,0; 49,92</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,4; 68,56</t>
+          <t>12,45; 67,33</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,52; 61,81</t>
+          <t>16,54; 61,73</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 37,56</t>
+          <t>-2,04; 40,62</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>10,54; 49,34</t>
+          <t>9,82; 51,51</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>1,17</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,75</t>
+          <t>1,66; 6,01</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,25</t>
+          <t>-1,55; 2,23</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 2,21</t>
+          <t>-1,25; 2,92</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,86; 8,42</t>
+          <t>3,96; 8,39</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 2,43</t>
+          <t>-1,91; 2,47</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 18,28</t>
+          <t>-0,8; 3,19</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,37</t>
+          <t>3,36; 6,36</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,61</t>
+          <t>-1,29; 1,66</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 10,09</t>
+          <t>-0,14; 2,65</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-1,47%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>8,72; 32,61</t>
+          <t>8,57; 33,9</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 12,76</t>
+          <t>-7,85; 12,79</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 12,46</t>
+          <t>-6,24; 16,8</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13,92; 32,96</t>
+          <t>14,14; 32,89</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 9,52</t>
+          <t>-6,84; 9,75</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 72,14</t>
+          <t>-3,01; 12,41</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,34; 29,08</t>
+          <t>14,25; 28,71</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 7,45</t>
+          <t>-5,5; 7,57</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 45,74</t>
+          <t>-0,61; 12,15</t>
         </is>
       </c>
     </row>
